--- a/branches/feat/newborn-screening-valuesets/ValueSet-mii-vs-seltene-nbs-hemoglobin-dbs.xlsx
+++ b/branches/feat/newborn-screening-valuesets/ValueSet-mii-vs-seltene-nbs-hemoglobin-dbs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:48:20+00:00</t>
+    <t>2026-08-28T15:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/feat/newborn-screening-valuesets/ValueSet-mii-vs-seltene-nbs-hemoglobin-dbs.xlsx
+++ b/branches/feat/newborn-screening-valuesets/ValueSet-mii-vs-seltene-nbs-hemoglobin-dbs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T15:01:21+00:00</t>
+    <t>2026-08-28T15:14:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Hämoglobin-Fraktionen in Trockenblut, bezogen auf das Gesamthämoglobin — die Messgrößen des Screenings auf Sichelzellkrankheit und weitere Hämoglobinopathien.</t>
+    <t>Hämoglobin-Fraktionen in Trockenblut, bezogen auf das Gesamthämoglobin — die Messgrößen des Screenings auf Sichelzellkrankheit und weitere Hämoglobinopathien. Abgeleitet aus der LOINC-SNOMED-Ontologie und deshalb deutlich unvollständig gegenüber LOINC (rund ein Drittel der DBS-Hämoglobin-Codes); für die lückenlose Menge siehe mii-vs-seltene-nbs-dbs-all.</t>
   </si>
   <si>
     <t>Purpose</t>
